--- a/documentation/Death data dictionary.xlsx
+++ b/documentation/Death data dictionary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NAIM001\github_repos\death-data-provisional\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24527E8C-C38D-425B-8DC2-CCDBA23D11A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B55F5928-A550-4EA6-8D62-6CF4BD133C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3194" uniqueCount="1124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3193" uniqueCount="1123">
   <si>
     <t>Notes</t>
   </si>
@@ -3119,9 +3119,6 @@
   </si>
   <si>
     <t>cmplt_fl</t>
-  </si>
-  <si>
-    <t>r</t>
   </si>
   <si>
     <t>Opioid analgesic contributed drug overdose death</t>
@@ -9977,7 +9974,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CE9AD5B-6984-4426-B920-B6171B7B4773}">
-  <dimension ref="A1:I442"/>
+  <dimension ref="A1:D442"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.7109375" bestFit="1" customWidth="1"/>
@@ -13169,7 +13166,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>553</v>
       </c>
@@ -13183,7 +13180,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>555</v>
       </c>
@@ -13197,7 +13194,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>557</v>
       </c>
@@ -13211,7 +13208,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>559</v>
       </c>
@@ -13225,7 +13222,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>561</v>
       </c>
@@ -13239,7 +13236,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>563</v>
       </c>
@@ -13253,7 +13250,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>565</v>
       </c>
@@ -13267,7 +13264,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>567</v>
       </c>
@@ -13280,11 +13277,8 @@
       <c r="D296" t="s">
         <v>495</v>
       </c>
-      <c r="I296" t="s">
-        <v>1027</v>
-      </c>
-    </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>569</v>
       </c>
@@ -13298,7 +13292,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>571</v>
       </c>
@@ -13312,7 +13306,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>549</v>
       </c>
@@ -13326,7 +13320,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>573</v>
       </c>
@@ -13340,7 +13334,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>575</v>
       </c>
@@ -13354,7 +13348,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>577</v>
       </c>
@@ -13368,7 +13362,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>579</v>
       </c>
@@ -13382,7 +13376,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>512</v>
       </c>
@@ -13502,7 +13496,7 @@
         <v>207</v>
       </c>
       <c r="C312" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="D312" t="s">
         <v>495</v>
@@ -13650,7 +13644,7 @@
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B323" t="s">
         <v>207</v>
@@ -13754,7 +13748,7 @@
         <v>207</v>
       </c>
       <c r="C330" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="D330" t="s">
         <v>495</v>
@@ -13986,13 +13980,13 @@
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B347" t="s">
+        <v>819</v>
+      </c>
+      <c r="C347" t="s">
         <v>1031</v>
-      </c>
-      <c r="B347" t="s">
-        <v>819</v>
-      </c>
-      <c r="C347" t="s">
-        <v>1032</v>
       </c>
       <c r="D347" t="s">
         <v>14</v>
@@ -14000,13 +13994,13 @@
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B348" t="s">
+        <v>819</v>
+      </c>
+      <c r="C348" t="s">
         <v>1033</v>
-      </c>
-      <c r="B348" t="s">
-        <v>819</v>
-      </c>
-      <c r="C348" t="s">
-        <v>1034</v>
       </c>
       <c r="D348" t="s">
         <v>14</v>
@@ -14014,13 +14008,13 @@
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B349" t="s">
+        <v>819</v>
+      </c>
+      <c r="C349" t="s">
         <v>1035</v>
-      </c>
-      <c r="B349" t="s">
-        <v>819</v>
-      </c>
-      <c r="C349" t="s">
-        <v>1036</v>
       </c>
       <c r="D349" t="s">
         <v>14</v>
@@ -14028,13 +14022,13 @@
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B350" t="s">
+        <v>819</v>
+      </c>
+      <c r="C350" t="s">
         <v>1037</v>
-      </c>
-      <c r="B350" t="s">
-        <v>819</v>
-      </c>
-      <c r="C350" t="s">
-        <v>1038</v>
       </c>
       <c r="D350" t="s">
         <v>14</v>
@@ -14042,13 +14036,13 @@
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B351" t="s">
+        <v>819</v>
+      </c>
+      <c r="C351" t="s">
         <v>1039</v>
-      </c>
-      <c r="B351" t="s">
-        <v>819</v>
-      </c>
-      <c r="C351" t="s">
-        <v>1040</v>
       </c>
       <c r="D351" t="s">
         <v>14</v>
@@ -14070,222 +14064,222 @@
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B353" t="s">
+        <v>819</v>
+      </c>
+      <c r="C353" t="s">
         <v>1041</v>
-      </c>
-      <c r="B353" t="s">
-        <v>819</v>
-      </c>
-      <c r="C353" t="s">
-        <v>1042</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B354" t="s">
         <v>819</v>
       </c>
       <c r="C354" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B355" t="s">
         <v>819</v>
       </c>
       <c r="C355" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B356" t="s">
         <v>819</v>
       </c>
       <c r="C356" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B357" t="s">
         <v>819</v>
       </c>
       <c r="C357" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B358" t="s">
         <v>819</v>
       </c>
       <c r="C358" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B359" t="s">
         <v>819</v>
       </c>
       <c r="C359" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B360" t="s">
         <v>819</v>
       </c>
       <c r="C360" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B361" t="s">
         <v>819</v>
       </c>
       <c r="C361" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B362" t="s">
         <v>819</v>
       </c>
       <c r="C362" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B363" t="s">
         <v>819</v>
       </c>
       <c r="C363" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B364" t="s">
         <v>819</v>
       </c>
       <c r="C364" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B365" t="s">
         <v>819</v>
       </c>
       <c r="C365" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B366" t="s">
         <v>819</v>
       </c>
       <c r="C366" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B367" t="s">
         <v>819</v>
       </c>
       <c r="C367" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B368" t="s">
         <v>819</v>
       </c>
       <c r="C368" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B369" t="s">
         <v>819</v>
       </c>
       <c r="C369" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B370" t="s">
         <v>819</v>
       </c>
       <c r="C370" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B371" t="s">
         <v>819</v>
       </c>
       <c r="C371" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B372" t="s">
         <v>819</v>
       </c>
       <c r="C372" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="D372" t="s">
         <v>693</v>
@@ -14293,7 +14287,7 @@
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B373" t="s">
         <v>819</v>
@@ -14304,7 +14298,7 @@
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="B374" t="s">
         <v>819</v>
@@ -14315,7 +14309,7 @@
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B375" t="s">
         <v>819</v>
@@ -14326,7 +14320,7 @@
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B376" t="s">
         <v>819</v>
@@ -14337,7 +14331,7 @@
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="B377" t="s">
         <v>819</v>
@@ -14348,7 +14342,7 @@
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="B378" t="s">
         <v>819</v>
@@ -14359,7 +14353,7 @@
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B379" t="s">
         <v>819</v>
@@ -14370,7 +14364,7 @@
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="B380" t="s">
         <v>819</v>
@@ -14381,7 +14375,7 @@
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B381" t="s">
         <v>819</v>
@@ -14392,7 +14386,7 @@
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="B382" t="s">
         <v>819</v>
@@ -14403,7 +14397,7 @@
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="B383" t="s">
         <v>819</v>
@@ -14414,7 +14408,7 @@
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B384" t="s">
         <v>819</v>
@@ -14425,7 +14419,7 @@
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B385" t="s">
         <v>819</v>
@@ -14436,7 +14430,7 @@
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B386" t="s">
         <v>819</v>
@@ -14447,7 +14441,7 @@
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B387" t="s">
         <v>819</v>
@@ -14458,7 +14452,7 @@
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="B388" t="s">
         <v>819</v>
@@ -14469,7 +14463,7 @@
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="B389" t="s">
         <v>819</v>
@@ -14480,7 +14474,7 @@
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="B390" t="s">
         <v>819</v>
@@ -14491,7 +14485,7 @@
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B391" t="s">
         <v>819</v>
@@ -14502,222 +14496,222 @@
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B392" t="s">
+        <v>819</v>
+      </c>
+      <c r="D392" t="s">
         <v>1081</v>
-      </c>
-      <c r="B392" t="s">
-        <v>819</v>
-      </c>
-      <c r="D392" t="s">
-        <v>1082</v>
       </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B393" t="s">
         <v>819</v>
       </c>
       <c r="D393" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="B394" t="s">
         <v>819</v>
       </c>
       <c r="D394" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="B395" t="s">
         <v>819</v>
       </c>
       <c r="D395" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="B396" t="s">
         <v>819</v>
       </c>
       <c r="D396" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="B397" t="s">
         <v>819</v>
       </c>
       <c r="D397" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="B398" t="s">
         <v>819</v>
       </c>
       <c r="D398" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="B399" t="s">
         <v>819</v>
       </c>
       <c r="D399" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B400" t="s">
         <v>819</v>
       </c>
       <c r="D400" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B401" t="s">
         <v>819</v>
       </c>
       <c r="D401" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B402" t="s">
         <v>819</v>
       </c>
       <c r="D402" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B403" t="s">
         <v>819</v>
       </c>
       <c r="D403" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="B404" t="s">
         <v>819</v>
       </c>
       <c r="D404" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="B405" t="s">
         <v>819</v>
       </c>
       <c r="D405" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B406" t="s">
         <v>819</v>
       </c>
       <c r="D406" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="B407" t="s">
         <v>819</v>
       </c>
       <c r="D407" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="B408" t="s">
         <v>819</v>
       </c>
       <c r="D408" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="B409" t="s">
         <v>819</v>
       </c>
       <c r="D409" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="B410" t="s">
         <v>819</v>
       </c>
       <c r="D410" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B411" t="s">
+        <v>819</v>
+      </c>
+      <c r="D411" t="s">
         <v>1101</v>
-      </c>
-      <c r="B411" t="s">
-        <v>819</v>
-      </c>
-      <c r="D411" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.25">
@@ -14728,38 +14722,38 @@
         <v>207</v>
       </c>
       <c r="C412" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="D412" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="B413" t="s">
         <v>207</v>
       </c>
       <c r="C413" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="D413" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B414" t="s">
+        <v>819</v>
+      </c>
+      <c r="C414" t="s">
         <v>1106</v>
       </c>
-      <c r="B414" t="s">
-        <v>819</v>
-      </c>
-      <c r="C414" t="s">
-        <v>1107</v>
-      </c>
       <c r="D414" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.25">
@@ -14773,7 +14767,7 @@
         <v>675</v>
       </c>
       <c r="D415" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.25">
@@ -14787,7 +14781,7 @@
         <v>678</v>
       </c>
       <c r="D416" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.25">
@@ -14801,35 +14795,35 @@
         <v>680</v>
       </c>
       <c r="D417" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B418" t="s">
+        <v>819</v>
+      </c>
+      <c r="C418" t="s">
         <v>1108</v>
       </c>
-      <c r="B418" t="s">
-        <v>819</v>
-      </c>
-      <c r="C418" t="s">
-        <v>1109</v>
-      </c>
       <c r="D418" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B419" t="s">
+        <v>819</v>
+      </c>
+      <c r="C419" t="s">
         <v>1110</v>
       </c>
-      <c r="B419" t="s">
-        <v>819</v>
-      </c>
-      <c r="C419" t="s">
-        <v>1111</v>
-      </c>
       <c r="D419" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.25">
@@ -14843,7 +14837,7 @@
         <v>682</v>
       </c>
       <c r="D420" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.25">
@@ -14857,7 +14851,7 @@
         <v>684</v>
       </c>
       <c r="D421" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.25">
@@ -14871,7 +14865,7 @@
         <v>686</v>
       </c>
       <c r="D422" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.25">
@@ -14885,7 +14879,7 @@
         <v>688</v>
       </c>
       <c r="D423" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.25">
@@ -14899,7 +14893,7 @@
         <v>667</v>
       </c>
       <c r="D424" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.25">
@@ -14910,10 +14904,10 @@
         <v>819</v>
       </c>
       <c r="C425" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="D425" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.25">
@@ -14927,7 +14921,7 @@
         <v>661</v>
       </c>
       <c r="D426" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.25">
@@ -14941,7 +14935,7 @@
         <v>663</v>
       </c>
       <c r="D427" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.25">
@@ -14952,10 +14946,10 @@
         <v>819</v>
       </c>
       <c r="C428" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="D428" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.25">
@@ -14966,10 +14960,10 @@
         <v>819</v>
       </c>
       <c r="C429" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="D429" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.25">
@@ -14980,10 +14974,10 @@
         <v>819</v>
       </c>
       <c r="C430" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="D430" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.25">
@@ -14997,21 +14991,21 @@
         <v>645</v>
       </c>
       <c r="D431" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B432" t="s">
+        <v>819</v>
+      </c>
+      <c r="C432" t="s">
         <v>1116</v>
       </c>
-      <c r="B432" t="s">
-        <v>819</v>
-      </c>
-      <c r="C432" t="s">
-        <v>1117</v>
-      </c>
       <c r="D432" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.25">
@@ -15025,7 +15019,7 @@
         <v>649</v>
       </c>
       <c r="D433" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="434" spans="1:4" x14ac:dyDescent="0.25">
@@ -15036,10 +15030,10 @@
         <v>819</v>
       </c>
       <c r="C434" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="D434" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.25">
@@ -15053,7 +15047,7 @@
         <v>655</v>
       </c>
       <c r="D435" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.25">
@@ -15064,10 +15058,10 @@
         <v>819</v>
       </c>
       <c r="C436" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="D436" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="437" spans="1:4" x14ac:dyDescent="0.25">
@@ -15078,10 +15072,10 @@
         <v>819</v>
       </c>
       <c r="C437" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="D437" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="438" spans="1:4" x14ac:dyDescent="0.25">
@@ -15095,7 +15089,7 @@
         <v>670</v>
       </c>
       <c r="D438" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.25">
@@ -15109,7 +15103,7 @@
         <v>672</v>
       </c>
       <c r="D439" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="440" spans="1:4" x14ac:dyDescent="0.25">
@@ -15120,10 +15114,10 @@
         <v>819</v>
       </c>
       <c r="C440" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="D440" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.25">
@@ -15134,10 +15128,10 @@
         <v>819</v>
       </c>
       <c r="C441" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="D441" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.25">
@@ -15148,10 +15142,10 @@
         <v>819</v>
       </c>
       <c r="C442" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="D442" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
   </sheetData>
@@ -15335,20 +15329,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <type xmlns="492fffa5-6dca-4100-8d29-96bcf255a1a6" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <type xmlns="492fffa5-6dca-4100-8d29-96bcf255a1a6" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -15370,14 +15364,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1616596F-C13B-4C4E-979E-C3F7E6204495}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C7076DA-C0B2-4FAA-8623-8EE1976CDADB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -15391,4 +15377,12 @@
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1616596F-C13B-4C4E-979E-C3F7E6204495}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>